--- a/daten/spieltag_02/auswertung_st02.xlsx
+++ b/daten/spieltag_02/auswertung_st02.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Spieltag'!$A$1:$O$7</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Elf je Manager'!$A$1:$R$67</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Protokoll'!$A$1:$C$8</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Protokoll'!$A$1:$C$9</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -3490,34 +3490,32 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Bellingham</t>
+          <t>Kade</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Dortmund</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="inlineStr">
-        <is>
-          <t>Nachrücker</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>Kade</t>
-        </is>
-      </c>
-      <c r="G52" t="n">
-        <v>3</v>
-      </c>
-      <c r="H52" t="n">
-        <v>4</v>
-      </c>
-      <c r="I52" t="inlineStr"/>
+          <t>Augsburg</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>Strafnote</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr"/>
+      <c r="G52" t="inlineStr"/>
+      <c r="H52" s="3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>ja</t>
+        </is>
+      </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>ja</t>
+          <t>nein</t>
         </is>
       </c>
       <c r="K52" t="inlineStr"/>
@@ -3596,29 +3594,31 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
+          <t>Bellingham</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>Dortmund</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>Nachrücker</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
           <t>Chaibi</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
-        <is>
-          <t>Frankfurt</t>
-        </is>
-      </c>
-      <c r="E54" t="inlineStr">
-        <is>
-          <t>Strafnote</t>
-        </is>
-      </c>
-      <c r="F54" t="inlineStr"/>
-      <c r="G54" t="inlineStr"/>
-      <c r="H54" s="3" t="n">
-        <v>5.5</v>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>ja</t>
-        </is>
-      </c>
+      <c r="G54" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" t="n">
+        <v>4</v>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="J54" t="inlineStr">
         <is>
           <t>ja</t>
@@ -4267,7 +4267,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -4390,7 +4390,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>MIT Kade: keine Note → Bellingham rückt nach (Bank 3).</t>
+          <t>Mehrere Ausfälle auf einer Position: Nachrücker werden in umgekehrter Aufstellungsreihenfolge vergeben (zuletzt genannter zuerst).</t>
         </is>
       </c>
     </row>
@@ -4407,12 +4407,29 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>MIT Chaibi: keine Note, kein Ersatz-MIT mit Note → Strafnote 5,5.</t>
+          <t>MIT Kade: nicht eingesetzt, kein Ersatz-MIT mit Note oder Einsatz → Strafnote 5,5.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Andreas</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Protokoll</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>MIT Chaibi: keine Note → Bellingham rückt nach (Bank 3).</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:C8"/>
+  <autoFilter ref="A1:C9"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>